--- a/ci-cd-merge-resolver/repoCollector/datasets/clickhouse-java.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/clickhouse-java.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,22 +44,31 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>0f5de183b9a3a3f509f94314da7db8f46dddd49c</t>
-  </si>
-  <si>
-    <t>6cc8b68491d7f2c1b30d622888ed75ed880edcf4</t>
-  </si>
-  <si>
-    <t>26da7d8a05fdd712dc45d780a1be515230d4b578</t>
-  </si>
-  <si>
-    <t>a265d08132600286e031ffb89537d430207798cf</t>
-  </si>
-  <si>
-    <t>9afa1c448907e23500a63b4ab656a6be38b6f537</t>
-  </si>
-  <si>
-    <t>8a4aee2081607c032bdef671778e2e10e07e8026</t>
+    <t>d2359e89ac7409dc049c4190aec0f5576d60d89f</t>
+  </si>
+  <si>
+    <t>41bccff2bb6e226a62613f2231870f6045d1bb4b</t>
+  </si>
+  <si>
+    <t>8e68aa489d21fcb4a0f4d48c05028f804f048169</t>
+  </si>
+  <si>
+    <t>411874fb12c433aafeaee7cffea54112bef3200c</t>
+  </si>
+  <si>
+    <t>cf9c610a71877019b86856e4d9f96a65ff2dab30</t>
+  </si>
+  <si>
+    <t>a90da544af6a71631fcca0f66a86589bf7a4f046</t>
+  </si>
+  <si>
+    <t>65f50635b62dc59de4262c36b861f0d89676f4f5</t>
+  </si>
+  <si>
+    <t>430deec4b06efcb9e1630ed347007d308bdde85b</t>
+  </si>
+  <si>
+    <t>6800fef492e8397b37822c06cbe16ec3e4abc043</t>
   </si>
 </sst>
 </file>
@@ -104,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -150,13 +159,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>288.0</v>
+        <v>545.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -165,10 +174,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>15.116000175476074</v>
+        <v>32.4119987487793</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -182,13 +191,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>288.0</v>
+        <v>858.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -197,10 +206,42 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>15.277000427246094</v>
+        <v>32.612998962402344</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>847.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>31.76300048828125</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
